--- a/base de datos/diccionario datos-v2.xlsx
+++ b/base de datos/diccionario datos-v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6fd9368643786761/Documentación actual para corrección - copia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="974" documentId="13_ncr:1_{915B43FA-E4D6-44FB-B9AA-7BC986674B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{765FB537-14D3-43E6-BB7A-A20921C8CB88}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4CD0DC55-1632-4F58-898E-B5C4B745801D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Historial de versiones" sheetId="34" r:id="rId1"/>
@@ -27,10 +27,10 @@
     <sheet name="estado_solicitud" sheetId="11" r:id="rId12"/>
     <sheet name="solicitud" sheetId="12" r:id="rId13"/>
     <sheet name="solicitud_desarrollador" sheetId="13" r:id="rId14"/>
-    <sheet name="historial_estado_solicitud" sheetId="14" r:id="rId15"/>
-    <sheet name="aprobacion_solicitud" sheetId="15" r:id="rId16"/>
-    <sheet name="comentario_solicitud" sheetId="16" r:id="rId17"/>
-    <sheet name="adjunto_solicitud" sheetId="17" r:id="rId18"/>
+    <sheet name="solicitud_historial_estado" sheetId="14" r:id="rId15"/>
+    <sheet name="solicitud_aprobacion" sheetId="15" r:id="rId16"/>
+    <sheet name="solicitud_comentario" sheetId="16" r:id="rId17"/>
+    <sheet name="solicitud_adjunto" sheetId="17" r:id="rId18"/>
     <sheet name="notificacion" sheetId="18" r:id="rId19"/>
     <sheet name="usuario_credencial" sheetId="19" r:id="rId20"/>
     <sheet name="menu_opcion" sheetId="20" r:id="rId21"/>
@@ -44,9 +44,10 @@
     <sheet name="proyecto" sheetId="28" r:id="rId29"/>
     <sheet name="proyecto_solicitud" sheetId="29" r:id="rId30"/>
     <sheet name="proyecto_miembro" sheetId="30" r:id="rId31"/>
-    <sheet name="documento_proyecto" sheetId="31" r:id="rId32"/>
-    <sheet name="evento_calendario" sheetId="32" r:id="rId33"/>
-    <sheet name="evento_participante" sheetId="33" r:id="rId34"/>
+    <sheet name="sistema_desarrollador" sheetId="39" r:id="rId32"/>
+    <sheet name="documento_proyecto" sheetId="31" r:id="rId33"/>
+    <sheet name="evento_calendario" sheetId="32" r:id="rId34"/>
+    <sheet name="evento_participante" sheetId="33" r:id="rId35"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -66,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1711" uniqueCount="567">
   <si>
     <t>Descripción</t>
   </si>
@@ -149,27 +150,15 @@
     <t>Asignación N:M de desarrolladores a solicitudes.</t>
   </si>
   <si>
-    <t>historial_estado_solicitud</t>
-  </si>
-  <si>
     <t>Histórico de cambios de estado de solicitud.</t>
   </si>
   <si>
-    <t>aprobacion_solicitud</t>
-  </si>
-  <si>
     <t>Registro de aprobaciones y rechazos.</t>
   </si>
   <si>
-    <t>comentario_solicitud</t>
-  </si>
-  <si>
     <t>Comentarios asociados a solicitudes.</t>
   </si>
   <si>
-    <t>adjunto_solicitud</t>
-  </si>
-  <si>
     <t>Archivos adjuntos de solicitudes.</t>
   </si>
   <si>
@@ -969,9 +958,6 @@
   </si>
   <si>
     <t xml:space="preserve">solicitud </t>
-  </si>
-  <si>
-    <t xml:space="preserve">comentario_solicitud </t>
   </si>
   <si>
     <t>Folio único de negocio.</t>
@@ -1620,10 +1606,6 @@
     <t>Fecha y hora en que se creó la relación entre proyecto y solicitud. Se registra automáticamente para fines de auditoría, seguimiento cronológico y análisis de evolución del alcance del proyecto.</t>
   </si>
   <si>
-    <t xml:space="preserve">La tabla proyecto_miembro administra la participación de usuarios dentro de cada proyecto. Define quién forma parte del equipo, qué rol operativo desempeña, qué porcentaje de carga estimada tiene asignado y durante qué periodo participa. Es clave para la planeación de capacidad, seguimiento de responsabilidades y control de vigencia de integrantes.
-</t>
-  </si>
-  <si>
     <t>Identificador técnico único del registro de membresía. Se genera automáticamente y permite referenciar cada asignación de usuario a proyecto de forma individual para auditoría, historial y mantenimiento.</t>
   </si>
   <si>
@@ -1747,13 +1729,61 @@
   <si>
     <t xml:space="preserve">La tabla proyecto es la entidad central para gestionar iniciativas de trabajo que agrupan múltiples solicitudes, equipo responsable, planificación y seguimiento ejecutivo. Permite controlar el ciclo de vida del proyecto, desde su planeación hasta su cierre, incluyendo fechas objetivo, responsable PM y vigencia lógica del registro.
 </t>
+  </si>
+  <si>
+    <t>sistema_desarrollador</t>
+  </si>
+  <si>
+    <t>solicitud_historial_estado</t>
+  </si>
+  <si>
+    <t>solicitud_aprobacion</t>
+  </si>
+  <si>
+    <t>solicitud_comentario</t>
+  </si>
+  <si>
+    <t>solicitud_adjunto</t>
+  </si>
+  <si>
+    <t>Registra la asignación de personal técnico a cada sistema institucional, indicando su rol de participación, vigencia y periodo de colaboración. Esta tabla resuelve la relación N:M entre sistema y usuario, permitiendo que un sistema tenga varios desarrolladores y que un desarrollador participe en varios sistemas. También soporta trazabilidad operativa para saber quién fue responsable, desde cuándo, y si la asignación sigue activa o ya concluyó.</t>
+  </si>
+  <si>
+    <t>sistema_desarrollador_id</t>
+  </si>
+  <si>
+    <t>Identificador técnico único de la asignación. Sirve como clave primaria para referenciar, auditar y actualizar el registro sin ambigüedad. No tiene significado de negocio, su función es integridad y trazabilidad.</t>
+  </si>
+  <si>
+    <t>Identificador del sistema al que se asigna el desarrollador. Define el contexto funcional de trabajo y garantiza que la asignación solo apunte a sistemas válidos registrados en el catálogo institucional.</t>
+  </si>
+  <si>
+    <t>Identificador del usuario técnico asignado al sistema. Permite vincular responsables y participantes reales, además de cruzar información con roles, áreas y actividad operativa del usuario.</t>
+  </si>
+  <si>
+    <t>Rol funcional del usuario dentro del sistema. Valores sugeridos: RESPONSABLE y PARTICIPANTE. RESPONSABLE implica liderazgo o accountability técnica; PARTICIPANTE implica apoyo en desarrollo, mantenimiento o atención de incidencias.</t>
+  </si>
+  <si>
+    <t>Bandera de vigencia lógica de la asignación. Valor 1 indica asignación vigente y operativa; valor 0 indica asignación cerrada o inactiva, conservando historial sin eliminar datos.</t>
+  </si>
+  <si>
+    <t>Fecha y hora en que inicia formalmente la participación del usuario en el sistema. Se usa para trazabilidad histórica, reportes de carga técnica y validación de periodos de responsabilidad.</t>
+  </si>
+  <si>
+    <t>Fecha y hora de término de la participación. Nulo indica participación vigente. Cuando tiene valor, marca cierre administrativo/técnico y permite análisis históricos de rotación y continuidad del equipo.</t>
+  </si>
+  <si>
+    <t>La tabla proyecto_miembro administra la participación de usuarios dentro de cada proyecto. Define quién forma parte del equipo, qué rol operativo desempeña, qué porcentaje de carga estimada tiene asignado y durante qué periodo participa. Es clave para la planeación de capacidad, seguimiento de responsabilidades y control de vigencia de integrantes.</t>
+  </si>
+  <si>
+    <t>Registra la asignación de usuarios a sistemas.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1804,6 +1834,12 @@
       <name val="Garamond"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1949,7 +1985,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2043,6 +2079,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2357,16 +2396,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2377,80 +2416,80 @@
         <v>46126</v>
       </c>
       <c r="C2" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="D2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B3" s="16">
         <v>45762</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="D3" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="B4" s="16">
         <v>46128</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B5" s="16">
         <v>46129</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B6" s="16">
         <v>46132</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B7" s="16">
         <v>46133</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -2461,24 +2500,24 @@
         <v>46134</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B9" s="16">
         <v>46135</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>
@@ -2502,7 +2541,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
         <v>17</v>
@@ -2518,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C2" s="38"/>
       <c r="D2" s="38"/>
@@ -2528,100 +2567,100 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="7" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="7" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="17">
         <v>1</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="G7" s="4"/>
     </row>
@@ -2650,7 +2689,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
         <v>19</v>
@@ -2666,7 +2705,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C2" s="38"/>
       <c r="D2" s="38"/>
@@ -2676,117 +2715,117 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="7" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="7" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="7" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E8" s="17">
         <v>1</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="G8" s="4"/>
     </row>
@@ -2815,7 +2854,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
         <v>21</v>
@@ -2831,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -2841,119 +2880,119 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="7" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="7" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="17">
         <v>0</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E8" s="17">
         <v>1</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="G8" s="4"/>
     </row>
@@ -2982,10 +3021,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
@@ -2998,7 +3037,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -3008,313 +3047,313 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="10" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="10" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="10" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="10" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="11" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="10" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="10" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="10" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="10" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="G14" s="4"/>
     </row>
     <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="10" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="G15" s="4"/>
     </row>
     <row r="16" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="4" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="10" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="G16" s="4"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="10" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="G17" s="4"/>
     </row>
     <row r="18" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E18" s="17">
         <v>1</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="G18" s="4"/>
     </row>
@@ -3344,7 +3383,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
         <v>25</v>
@@ -3360,7 +3399,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -3370,159 +3409,159 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="7" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="7" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="9"/>
       <c r="B7" s="9" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="7" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="9" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E8" s="17">
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="9"/>
       <c r="B9" s="9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="9"/>
       <c r="B10" s="9" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="7" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="G10" s="4"/>
     </row>
@@ -3551,10 +3590,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>27</v>
+        <v>552</v>
       </c>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
@@ -3567,7 +3606,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -3577,165 +3616,165 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="9" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="9" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="9" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A8" s="15"/>
       <c r="B8" s="15" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="9" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="G8" s="15"/>
     </row>
     <row r="9" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="9" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A10" s="15"/>
       <c r="B10" s="15" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="G10" s="4"/>
     </row>
@@ -3764,10 +3803,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>29</v>
+        <v>553</v>
       </c>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
@@ -3780,7 +3819,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -3790,140 +3829,140 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="G4" s="9"/>
     </row>
     <row r="5" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="9" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6" s="9" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A7" s="9"/>
       <c r="B7" s="9" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="G7" s="9"/>
     </row>
     <row r="8" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="9" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="9" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="G8" s="9"/>
     </row>
     <row r="9" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A9" s="9"/>
       <c r="B9" s="9" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="G9" s="9"/>
     </row>
@@ -3952,10 +3991,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>301</v>
+        <v>554</v>
       </c>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
@@ -3968,7 +4007,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -3978,142 +4017,142 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="G4" s="13"/>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="23" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="23" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="13"/>
       <c r="B7" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C7" s="13" t="s">
-        <v>142</v>
-      </c>
       <c r="D7" s="13" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="13"/>
       <c r="F7" s="23" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="G7" s="13"/>
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="13"/>
       <c r="B8" s="13" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E8" s="24">
         <v>0</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="G8" s="13"/>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="13"/>
       <c r="B9" s="13" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="G9" s="13"/>
     </row>
@@ -4142,10 +4181,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>33</v>
+        <v>555</v>
       </c>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
@@ -4158,7 +4197,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C2" s="38"/>
       <c r="D2" s="38"/>
@@ -4168,174 +4207,174 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="G4" s="10"/>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="10"/>
       <c r="F5" s="10" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="10"/>
       <c r="B6" s="10" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="10" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="G6" s="10"/>
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="10" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="10"/>
       <c r="F7" s="10" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G7" s="10"/>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="10"/>
       <c r="B8" s="10" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="10" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="G8" s="10"/>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="10"/>
       <c r="B9" s="10" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="10" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="10" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
       <c r="B11" s="10" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="G11" s="10"/>
     </row>
@@ -4437,10 +4476,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
@@ -4453,7 +4492,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -4463,176 +4502,176 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="21" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="9" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="9" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="9" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
       <c r="B8" s="7" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="9" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="G8" s="7"/>
     </row>
     <row r="9" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="7" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E9" s="25">
         <v>0</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" s="9" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="B11" s="9" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="G11" s="7"/>
     </row>
@@ -4647,21 +4686,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:D34"/>
+  <dimension ref="A2:I35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.85546875" customWidth="1"/>
     <col min="2" max="2" width="64.85546875" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" customWidth="1"/>
     <col min="4" max="4" width="34.85546875" customWidth="1"/>
+    <col min="8" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" customWidth="1"/>
+    <col min="11" max="11" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>1</v>
@@ -4708,7 +4750,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="13">
-        <f t="shared" ref="C5:C34" ca="1" si="0">IFERROR(COUNTA(INDIRECT("'"&amp;D5&amp;"'!B4:B55")),0)</f>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D5&amp;"'!B4:B55")),0)</f>
         <v>5</v>
       </c>
       <c r="D5" s="32" t="s">
@@ -4723,7 +4765,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D6&amp;"'!B4:B55")),0)</f>
         <v>8</v>
       </c>
       <c r="D6" s="32" t="s">
@@ -4738,7 +4780,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D7&amp;"'!B4:B55")),0)</f>
         <v>7</v>
       </c>
       <c r="D7" s="32" t="s">
@@ -4753,7 +4795,7 @@
         <v>14</v>
       </c>
       <c r="C8" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D8&amp;"'!B4:B55")),0)</f>
         <v>6</v>
       </c>
       <c r="D8" s="32" t="s">
@@ -4768,7 +4810,7 @@
         <v>16</v>
       </c>
       <c r="C9" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D9&amp;"'!B4:B55")),0)</f>
         <v>5</v>
       </c>
       <c r="D9" s="32" t="s">
@@ -4783,7 +4825,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D10&amp;"'!B4:B55")),0)</f>
         <v>4</v>
       </c>
       <c r="D10" s="32" t="s">
@@ -4798,7 +4840,7 @@
         <v>20</v>
       </c>
       <c r="C11" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D11&amp;"'!B4:B55")),0)</f>
         <v>5</v>
       </c>
       <c r="D11" s="32" t="s">
@@ -4813,7 +4855,7 @@
         <v>22</v>
       </c>
       <c r="C12" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D12&amp;"'!B4:B55")),0)</f>
         <v>5</v>
       </c>
       <c r="D12" s="32" t="s">
@@ -4828,7 +4870,7 @@
         <v>24</v>
       </c>
       <c r="C13" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D13&amp;"'!B4:B55")),0)</f>
         <v>15</v>
       </c>
       <c r="D13" s="32" t="s">
@@ -4843,7 +4885,7 @@
         <v>26</v>
       </c>
       <c r="C14" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D14&amp;"'!B4:B55")),0)</f>
         <v>7</v>
       </c>
       <c r="D14" s="32" t="s">
@@ -4852,302 +4894,317 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
+        <v>552</v>
+      </c>
+      <c r="B15" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="13" t="s">
-        <v>28</v>
-      </c>
       <c r="C15" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D15&amp;"'!B4:B55")),0)</f>
         <v>7</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>27</v>
+        <v>552</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>29</v>
+        <v>553</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C16" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D16&amp;"'!B4:B55")),0)</f>
         <v>6</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>29</v>
+        <v>553</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>31</v>
+        <v>554</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C17" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D17&amp;"'!B4:B55")),0)</f>
         <v>6</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>31</v>
+        <v>554</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>33</v>
+        <v>555</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C18" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D18&amp;"'!B4:B55")),0)</f>
         <v>8</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>33</v>
+        <v>555</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C19" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D19&amp;"'!B4:B55")),0)</f>
         <v>8</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C20" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D20&amp;"'!B4:B55")),0)</f>
         <v>11</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C21" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D21&amp;"'!B4:B55")),0)</f>
         <v>8</v>
       </c>
       <c r="D21" s="32" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C22" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D22&amp;"'!B4:B55")),0)</f>
         <v>6</v>
       </c>
       <c r="D22" s="32" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C23" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D23&amp;"'!B4:B55")),0)</f>
         <v>4</v>
       </c>
       <c r="D23" s="32" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C24" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D24&amp;"'!B4:B55")),0)</f>
         <v>8</v>
       </c>
       <c r="D24" s="32" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C25" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D25&amp;"'!B4:B55")),0)</f>
         <v>11</v>
       </c>
       <c r="D25" s="32" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C26" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D26&amp;"'!B4:B55")),0)</f>
         <v>11</v>
       </c>
       <c r="D26" s="32" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C27" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D27&amp;"'!B4:B55")),0)</f>
         <v>11</v>
       </c>
       <c r="D27" s="32" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C28" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D28&amp;"'!B4:B55")),0)</f>
         <v>10</v>
       </c>
       <c r="D28" s="32" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C29" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D29&amp;"'!B4:B55")),0)</f>
         <v>10</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C30" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D30&amp;"'!B4:B55")),0)</f>
         <v>4</v>
       </c>
       <c r="D30" s="32" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C31" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D31&amp;"'!B4:B55")),0)</f>
         <v>8</v>
       </c>
       <c r="D31" s="32" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>62</v>
+        <v>551</v>
+      </c>
+      <c r="B32" s="40" t="s">
+        <v>566</v>
       </c>
       <c r="C32" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D32&amp;"'!B4:B55")),0)</f>
+        <v>7</v>
       </c>
       <c r="D32" s="32" t="s">
-        <v>61</v>
+        <v>551</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C33" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D33&amp;"'!B4:B55")),0)</f>
+        <v>11</v>
       </c>
       <c r="D33" s="32" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C34" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D34&amp;"'!B4:B55")),0)</f>
+        <v>10</v>
+      </c>
+      <c r="D34" s="32" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" s="13">
+        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D35&amp;"'!B4:B55")),0)</f>
         <v>4</v>
       </c>
-      <c r="D34" s="32" t="s">
-        <v>65</v>
+      <c r="D35" s="32" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -5164,10 +5221,10 @@
     <hyperlink ref="D12" location="estado_solicitud!A1" display="estado_solicitud" xr:uid="{1F073571-531A-4F1B-A954-5DDF15E6A1C9}"/>
     <hyperlink ref="D13" location="solicitud!A1" display="solicitud" xr:uid="{632C16CC-3B6E-48E3-8D34-6C8DDE3803B4}"/>
     <hyperlink ref="D14" location="'solicitud_desarrollador'!A1" display="solicitud_desarrollador" xr:uid="{74970300-8BD4-42BA-BF7C-880FC2F65753}"/>
-    <hyperlink ref="D15" location="historial_estado_solicitud!A1" display="historial_estado_solicitud" xr:uid="{242F7E10-6D13-44A7-8FA4-026C89728791}"/>
-    <hyperlink ref="D16" location="aprobacion_solicitud!A1" display="aprobacion_solicitud" xr:uid="{B093588F-7E4E-43D4-93F8-21380A0EF26D}"/>
-    <hyperlink ref="D17" location="comentario_solicitud!A1" display="comentario_solicitud" xr:uid="{D2F3E127-2BAF-49DD-9250-B1B182FB42BF}"/>
-    <hyperlink ref="D18" location="adjunto_solicitud!A1" display="adjunto_solicitud" xr:uid="{C256EC25-1819-4E94-A290-CE63736A8BBB}"/>
+    <hyperlink ref="D15" location="solicitud_historial_estado!A1" display="solicitud_historial_estado" xr:uid="{242F7E10-6D13-44A7-8FA4-026C89728791}"/>
+    <hyperlink ref="D16" location="solicitud_aprobacion!A1" display="solicitud_aprobacion" xr:uid="{B093588F-7E4E-43D4-93F8-21380A0EF26D}"/>
+    <hyperlink ref="D17" location="solicitud_comentario!A1" display="solicitud_comentario" xr:uid="{D2F3E127-2BAF-49DD-9250-B1B182FB42BF}"/>
+    <hyperlink ref="D18" location="solicitud_adjunto!A1" display="solicitud_adjunto" xr:uid="{C256EC25-1819-4E94-A290-CE63736A8BBB}"/>
     <hyperlink ref="D19" location="notificacion!A1" display="notificacion" xr:uid="{0A5FDBCB-4F45-4BFA-809C-5C86F9F68072}"/>
     <hyperlink ref="D20" location="usuario_credencial!A1" display="usuario_credencial" xr:uid="{6DCD632A-A57E-498E-8C09-B502DF634D2D}"/>
     <hyperlink ref="D21" location="menu_opcion!A1" display="menu_opcion" xr:uid="{4487E834-90EB-4CB1-BA2B-EF51886DFA66}"/>
@@ -5181,9 +5238,10 @@
     <hyperlink ref="D29" location="proyecto!A1" display="proyecto" xr:uid="{0215288B-2E91-4CFB-B049-6FE438EEDBCF}"/>
     <hyperlink ref="D30" location="proyecto_solicitud!A1" display="proyecto_solicitud" xr:uid="{7006D0C4-1325-443E-921A-51685992685F}"/>
     <hyperlink ref="D31" location="proyecto_miembro!A1" display="proyecto_miembro" xr:uid="{A80B0950-37B5-4D7E-9B42-696F6382A1F2}"/>
-    <hyperlink ref="D32" location="documento_proyecto!A1" display="documento_proyecto" xr:uid="{0808F433-6682-4B84-95C8-51AC0C062DD1}"/>
-    <hyperlink ref="D34" location="evento_participante!A1" display="evento_participante" xr:uid="{70A16F5F-9B82-4A64-9262-91F18251F6DC}"/>
-    <hyperlink ref="D33" location="evento_calendario!A1" display="evento_calendario" xr:uid="{DFC53FFB-E375-46CF-9532-85DA4ADF49D7}"/>
+    <hyperlink ref="D33" location="documento_proyecto!A1" display="documento_proyecto" xr:uid="{0808F433-6682-4B84-95C8-51AC0C062DD1}"/>
+    <hyperlink ref="D35" location="evento_participante!A1" display="evento_participante" xr:uid="{70A16F5F-9B82-4A64-9262-91F18251F6DC}"/>
+    <hyperlink ref="D34" location="evento_calendario!A1" display="evento_calendario" xr:uid="{DFC53FFB-E375-46CF-9532-85DA4ADF49D7}"/>
+    <hyperlink ref="D32" location="sistema_desarrollador!A1" display="sistema_desarrollador" xr:uid="{DAB7F0B9-F482-4DA8-868D-D78D6B0583BF}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5207,10 +5265,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
@@ -5223,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C2" s="39"/>
       <c r="D2" s="39"/>
@@ -5233,227 +5291,227 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="26"/>
       <c r="F4" s="5" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="7" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="7" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="7" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="7" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="7" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="G12" s="4"/>
     </row>
     <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="G13" s="4"/>
     </row>
     <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="G14" s="4"/>
     </row>
@@ -5482,10 +5540,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
@@ -5498,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="C2" s="38"/>
       <c r="D2" s="38"/>
@@ -5508,173 +5566,173 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="27" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="G4" s="14"/>
     </row>
     <row r="5" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="9" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="G5" s="14"/>
     </row>
     <row r="6" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="9" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="G6" s="14"/>
     </row>
     <row r="7" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="9" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="G7" s="14"/>
     </row>
     <row r="8" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="9" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="G8" s="14"/>
     </row>
     <row r="9" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="9" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="G9" s="14"/>
     </row>
     <row r="10" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E10" s="17">
         <v>1</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="G10" s="31"/>
     </row>
     <row r="11" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="30" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -5702,10 +5760,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
@@ -5718,7 +5776,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C2" s="38"/>
       <c r="D2" s="38"/>
@@ -5728,144 +5786,144 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>444</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>445</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="17">
         <v>1</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E8" s="17">
         <v>0</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E9" s="17">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="G9" s="4"/>
     </row>
@@ -5894,10 +5952,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
@@ -5910,7 +5968,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="C2" s="38"/>
       <c r="D2" s="38"/>
@@ -5920,100 +5978,100 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="7" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="7" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="17">
         <v>1</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="G7" s="4"/>
     </row>
@@ -6042,10 +6100,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
@@ -6058,7 +6116,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -6068,174 +6126,174 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="7" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="7" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="7" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="7" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="7" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="7" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="G11" s="4"/>
     </row>
@@ -6264,10 +6322,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
@@ -6280,7 +6338,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -6290,225 +6348,225 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="7" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="7" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="7" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="7" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="7" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="7" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="7" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="7" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="G12" s="4"/>
     </row>
     <row r="13" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="7" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F14" s="29" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="G14" s="4"/>
     </row>
@@ -6537,10 +6595,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
@@ -6553,7 +6611,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -6563,229 +6621,229 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="7" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="7" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="7" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="7" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="7" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="7" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="7" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="7" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="G12" s="4"/>
     </row>
     <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="7" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E14" s="17">
         <v>1</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="G14" s="4"/>
     </row>
@@ -6814,10 +6872,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
@@ -6830,7 +6888,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -6840,229 +6898,229 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="7" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="7" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="7" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="7" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="7" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="7" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="7" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="7" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="G12" s="4"/>
     </row>
     <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="7" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E14" s="4">
         <v>1</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="G14" s="4"/>
     </row>
@@ -7091,10 +7149,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
@@ -7107,7 +7165,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -7117,216 +7175,216 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="7" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="7" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="7" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="7" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="7" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="7" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E12" s="17">
         <v>1</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="G12" s="4"/>
     </row>
     <row r="13" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E13" s="17">
         <v>1</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="G13" s="4"/>
     </row>
@@ -7355,10 +7413,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
@@ -7371,7 +7429,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -7381,206 +7439,206 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="7" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="7" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="7" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="7" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="7" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="7" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="7" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="7" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E13" s="17">
         <v>1</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="G13" s="4"/>
     </row>
@@ -7609,7 +7667,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
         <v>3</v>
@@ -7625,7 +7683,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
@@ -7635,142 +7693,142 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="6" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="6" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="6" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E8" s="17">
         <v>1</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="G9" s="4"/>
     </row>
@@ -7799,10 +7857,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
@@ -7815,7 +7873,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -7825,106 +7883,106 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="7" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="7" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="G7" s="4"/>
     </row>
@@ -7953,10 +8011,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
@@ -7969,7 +8027,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>516</v>
+        <v>565</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -7979,176 +8037,176 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="7" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="7" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="7" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="7" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E9" s="17">
         <v>1</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="7" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="G11" s="4"/>
     </row>
@@ -8158,10 +8216,219 @@
     <mergeCell ref="B2:G2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA7E44C4-E4B6-4DCC-BE19-C7DF38E6CEDD}">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="65" customWidth="1"/>
+    <col min="7" max="7" width="35.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>551</v>
+      </c>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+    </row>
+    <row r="2" spans="1:7" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+      <c r="A7" s="7"/>
+      <c r="B7" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="G7" s="7"/>
+    </row>
+    <row r="8" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="7"/>
+      <c r="B8" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E8" s="9">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="G8" s="7"/>
+    </row>
+    <row r="9" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="7"/>
+      <c r="B9" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>563</v>
+      </c>
+      <c r="G9" s="7"/>
+    </row>
+    <row r="10" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+      <c r="A10" s="7"/>
+      <c r="B10" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="G10" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8177,10 +8444,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
@@ -8193,7 +8460,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8203,231 +8470,231 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="7" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="7" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="7" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="7" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="7" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="7" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="7" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="7" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="G13" s="4"/>
     </row>
     <row r="14" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E14" s="17">
         <v>1</v>
       </c>
       <c r="F14" s="29" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="G14" s="4"/>
     </row>
@@ -8440,7 +8707,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8456,10 +8723,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
@@ -8472,7 +8739,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8482,212 +8749,212 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="7" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="7" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="7" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="7" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="7" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="7" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="7" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="7" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E13" s="17">
         <v>0</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="G13" s="4"/>
     </row>
@@ -8700,7 +8967,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8716,10 +8983,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
@@ -8732,7 +8999,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8742,98 +9009,98 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="7" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="7" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="7" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="7" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="G7" s="4"/>
     </row>
@@ -8862,7 +9129,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
         <v>5</v>
@@ -8878,7 +9145,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8888,170 +9155,170 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="8" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="8" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="8" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="8" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="8" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E10" s="17">
         <v>1</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G11" s="4"/>
     </row>
@@ -9080,7 +9347,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
         <v>7</v>
@@ -9096,7 +9363,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -9106,125 +9373,125 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="7" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="7" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="17">
         <v>1</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G8" s="4"/>
     </row>
@@ -9253,7 +9520,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
         <v>9</v>
@@ -9269,7 +9536,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -9279,174 +9546,174 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6" s="8" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="8" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="9" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="8" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="9" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="8" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E10" s="18">
         <v>1</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="G11" s="4"/>
     </row>
@@ -9475,7 +9742,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
         <v>11</v>
@@ -9491,7 +9758,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -9501,161 +9768,161 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="17"/>
       <c r="F5" s="7" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>102</v>
-      </c>
       <c r="C6" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="17"/>
       <c r="F6" s="7" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="17">
         <v>0</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E8" s="17">
         <v>1</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E10" s="17"/>
       <c r="F10" s="7" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G10" s="4"/>
     </row>
@@ -9684,7 +9951,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
         <v>13</v>
@@ -9700,7 +9967,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -9710,134 +9977,134 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="7" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="7" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="7" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E8" s="17">
         <v>1</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G9" s="4"/>
     </row>
@@ -9866,7 +10133,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="33" t="s">
         <v>15</v>
@@ -9882,7 +10149,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -9892,125 +10159,125 @@
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>102</v>
-      </c>
       <c r="C5" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="7" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="7" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="17">
         <v>1</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="G8" s="4"/>
     </row>
@@ -10024,18 +10291,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10201,6 +10468,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D579197-D438-4EF6-9CBD-9164EE63483F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E602F4C4-2459-471B-AF18-AA406C041954}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -10212,14 +10487,6 @@
     <ds:schemaRef ds:uri="6bcc5027-7626-4b3f-a1b8-943f1b440c70"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D579197-D438-4EF6-9CBD-9164EE63483F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
